--- a/backend/tests/data/test_results.xlsx
+++ b/backend/tests/data/test_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="16800" windowHeight="6096"/>
+    <workbookView windowWidth="16800" windowHeight="6048"/>
   </bookViews>
   <sheets>
     <sheet name="TestResults" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="47">
   <si>
     <t>input_id</t>
   </si>
@@ -111,6 +111,63 @@
   </si>
   <si>
     <t>NV Tour - fullname tiếng Việt có dấu</t>
+  </si>
+  <si>
+    <t>Fullname 2 ký tự (dưới min backend 3)</t>
+  </si>
+  <si>
+    <t>Fullname 3 ký tự (min backend)</t>
+  </si>
+  <si>
+    <t>Fullname 254 ký tự (gần max DB 255)</t>
+  </si>
+  <si>
+    <t>Fullname chỉ chứa số (JS validation block)</t>
+  </si>
+  <si>
+    <t>SĐT 8 số (thiếu - không match regex)</t>
+  </si>
+  <si>
+    <t>SĐT 11 số (dư - không match regex)</t>
+  </si>
+  <si>
+    <t>SĐT không bắt đầu bằng 0</t>
+  </si>
+  <si>
+    <t>SĐT chứa ký tự đặc biệt (gạch ngang)</t>
+  </si>
+  <si>
+    <t>Email thiếu TLD (.com / .vn)</t>
+  </si>
+  <si>
+    <t>Email thiếu local part (@.com)</t>
+  </si>
+  <si>
+    <t>Email chứa @@</t>
+  </si>
+  <si>
+    <t>Mật khẩu 1 ký tự (dưới min 6)</t>
+  </si>
+  <si>
+    <t>Mật khẩu 5 ký tự (dưới min 6)</t>
+  </si>
+  <si>
+    <t>Mật khẩu 6 ký tự (min)</t>
+  </si>
+  <si>
+    <t>Mật khẩu 7 ký tự (trên min)</t>
+  </si>
+  <si>
+    <t>Mật khẩu chỉ chứa số (vẫn hợp lệ)</t>
+  </si>
+  <si>
+    <t>Xác nhận mật khẩu để trống</t>
+  </si>
+  <si>
+    <t>Email đã tồn tại (trùng admin@gmail.com)</t>
+  </si>
+  <si>
+    <t>Fullname có khoảng trắng đầu/cuối (trim)</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.8333333333333" customWidth="1"/>
@@ -1549,11 +1606,391 @@
         <v>9</v>
       </c>
     </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="b">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="b">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="b">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="b">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34" t="b">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35" t="b">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>36</v>
+      </c>
+      <c r="B36" t="b">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>37</v>
+      </c>
+      <c r="B37" t="b">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>38</v>
+      </c>
+      <c r="B38" t="b">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>39</v>
+      </c>
+      <c r="B39" t="b">
+        <v>0</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>40</v>
+      </c>
+      <c r="B40" t="b">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>41</v>
+      </c>
+      <c r="B41" t="b">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F1 A2:C3 A4:F22" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1 A2:C3 A4:F41" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>